--- a/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
@@ -1856,6 +1856,26 @@
           <t>o comitê de tecnologia da informação realiza as atividades previstas em ato constitutivo</t>
         </is>
       </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia que a evidência é insuficiente. Apesar de a política determinar a elaboração de objetivos, metas e indicadores, não foram apresentados os planos estratégicos ou documentos equivalentes onde tais elementos tenham sido efetivamente estabelecidos. Há lacuna quanto à materialização dos objetivos e metas de gestão de TI.</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>estabeleceu objetivos, indicadores e metas para a gestão de tecnologia da informação</t>
+        </is>
+      </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -2077,26 +2097,6 @@
           <t>ARMAÇÃO DOS BÚZIOS</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>A evidência apresentada (Lei Ordinária nº 1.803/2023) trata exclusivamente da criação e transformação de cargos em comissão (CC) na estrutura administrativa do município. Não foram fornecidos documentos, como planos de cargos ou editais, que comprovem a existência de cargos efetivos (de carreira) voltados à área de tecnologia da informação. A evidência é insuficiente por não conter elementos que confirmem a existência de cargos de provimento permanente.</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos efetivos em tecnologia da informação</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2104,26 +2104,6 @@
           <t>ARRAIAL DO CABO</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>A avaliação indica que não há evidências suficientes para confirmar a realização das atividades previstas. O documento apresentado limita-se ao ato constitutivo do comitê (Lei Municipal nº 2.623/2025), sem apresentação de registros de reuniões, atas ou relatórios que demonstrem a execução das atribuições definidas. É necessária a apresentação de evidências da atuação prática do comitê para atender ao item.</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>o comitê de tecnologia da informação realiza as atividades previstas em ato constitutivo</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2325,26 +2305,6 @@
           <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CM10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CN10" t="inlineStr">
-        <is>
-          <t>As responsabilidades e atribuições das ocupações da área de tecnologia da informação não estão documentadas na evidência enviada. O documento restringe-se a uma tabela de cargos com símbolos de remuneração publicada no Diário Oficial. A avaliação realizada aponta a ausência de ato normativo, manual ou descritivo contendo as atribuições específicas para essas funções. Faltam registros documentais que definam claramente as responsabilidades de cada cargo de tecnologia da informação.</t>
-        </is>
-      </c>
-      <c r="CO10" t="inlineStr">
-        <is>
-          <t>as responsabilidades e atribuições das ocupações ou grupo de ocupações da área de tecnologia da informação estão definidas, documentadas e publicadas</t>
-        </is>
-      </c>
       <c r="CP10" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -2626,26 +2586,6 @@
           <t>os processos de trabalho e os artefatos padronizados estão aderentes às normas legais e infralegais que regem as contratações públicas</t>
         </is>
       </c>
-      <c r="DV13" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="DW13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="DX13" t="inlineStr">
-        <is>
-          <t>O documento apresentado disciplina o fluxo de projetos e a tramitação processual no SEI, mas não descreve papéis e responsabilidades da área de gestão de TI da organização. A evidência é insuficiente, pois inexiste ato normativo ou documento que defina as atribuições e competências estruturais da equipe de TI. Falta a apresentação de organograma ou descrição formal de cargos da área.</t>
-        </is>
-      </c>
-      <c r="DY13" t="inlineStr">
-        <is>
-          <t>define os papéis e responsabilidades da área de gestão de tecnologia da informação</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2833,26 +2773,6 @@
           <t>os processos de trabalho e os artefatos padronizados estão aderentes às normas legais e infralegais que regem as contratações públicas</t>
         </is>
       </c>
-      <c r="DZ14" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="EA14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="EB14" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que a evidência é insuficiente para comprovar o requisito. O material apresentado limita-se a registros de incidentes individuais, sem demonstrar a existência de uma base de conhecimento estruturada ou repositório de erros conhecidos para apoiar a resolução de demandas de forma eficiente. A ausência de elementos que atestem a presença de artigos, soluções mapeadas ou procedimentos reutilizáveis configura a inconformidade. Requer-se a apresentação de evidência de um repositório de conhecimento consultável.</t>
-        </is>
-      </c>
-      <c r="EC14" t="inlineStr">
-        <is>
-          <t>há base(s) de conhecimento que registra(m) erros conhecidos e problemas, de modo a tornar eficiente e efetiva a resolução de incidentes</t>
-        </is>
-      </c>
       <c r="ED14" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -2891,26 +2811,6 @@
       <c r="EK14" t="inlineStr">
         <is>
           <t>definiu responsabilidades pelos ativos associados à informação</t>
-        </is>
-      </c>
-      <c r="EL14" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="EM14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="EN14" t="inlineStr">
-        <is>
-          <t>Não há evidências que demonstrem o monitoramento da participação efetiva nas ações de capacitação listadas. O documento de planejamento apenas relaciona os participantes designados previamente, sem comprovação documental de frequência, relatórios de conclusão ou certificados de participação (páginas 1 a 6). A ausência de registros de presença ou indicadores de resultados das ações configura lacuna relevante.</t>
-        </is>
-      </c>
-      <c r="EO14" t="inlineStr">
-        <is>
-          <t>monitora a participação dos colaboradores e gestores nas ações de capacitação existentes</t>
         </is>
       </c>
     </row>
@@ -3114,26 +3014,6 @@
           <t>CGE</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Embora o tratamento operacional de incidentes de segurança esteja evidenciado por meio de registros de remediação, não há documentação comprovando os procedimentos para notificação formal de incidentes de segurança, nem as diretrizes de comunicação interna e externa exigidas. A ausência desses elementos impede a conformidade integral com o critério estabelecido.</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa</t>
-        </is>
-      </c>
       <c r="AD17" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -3154,26 +3034,6 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>Não foi demonstrada a existência de uma base de dados de configuração (CMDB) ou inventário equivalente que consolide as configurações e relacionamentos dos ativos de TI. Os relatórios anexados referem-se exclusivamente a análises de vulnerabilidades de segurança e não contêm informações sobre o mapeamento de configurações ou ativos tecnológicos. A ausência de um repositório centralizado impede a verificação da conformidade com o requisito de manutenção de base de dados de configuração.</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
-        </is>
-      </c>
       <c r="AL17" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -3194,26 +3054,6 @@
           <t>a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>Não foi demonstrado que o planejamento de contratações sirva de fundamento para a proposta orçamentária da organização. Embora o PEDTIC apresente a tabela 'Despesas Planejadas PEDTIC - 2025' (p. 16), com previsão de gastos e alinhamento à LOA, a evidência indica que o orçamento é um insumo para o PEDTIC, e não que o planejamento de contratações preceda ou baseie a proposta orçamentária. Ausente a comprovação da relação direta entre o PCA e o fundamento da proposta da Lei Orçamentária Anual.</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>o PCA fundamenta a proposta orçamentária da organização</t>
-        </is>
-      </c>
       <c r="BJ17" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -3234,26 +3074,6 @@
           <t>possui em sua estrutura cargos efetivos em tecnologia da informação</t>
         </is>
       </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>A evidência comprova a existência de critérios de priorização baseados em urgência e impacto, com geração automática de matriz de prioridade. Entretanto, não foram apresentados documentos ou registros que estabeleçam formalmente os procedimentos de escalamento de incidentes, como níveis hierárquicos, prazos ou gatilhos para movimentação entre grupos técnicos.</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>definiu regras para a priorização e o escalamento de incidentes</t>
-        </is>
-      </c>
       <c r="BR17" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -3274,26 +3094,6 @@
           <t>gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
         </is>
       </c>
-      <c r="BV17" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>Não é possível verificar se o PCA considera os demais instrumentos de planejamento da organização, visto que o PCA não foi apresentado. O PEDTIC demonstra, nas páginas 4, 13 e 14, estar em consonância com o Plano Estratégico (PEI), o Plano Plurianual (PPA) e a Lei Orçamentária Anual (LOA), contudo, tal integração é restrita ao plano de tecnologia da informação. Inexiste evidência da articulação entre o plano de contratações e os instrumentos de planejamento institucional.</t>
-        </is>
-      </c>
-      <c r="BY17" t="inlineStr">
-        <is>
-          <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
-        </is>
-      </c>
       <c r="BZ17" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -3512,26 +3312,6 @@
       <c r="EW17" t="inlineStr">
         <is>
           <t>os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado</t>
-        </is>
-      </c>
-      <c r="EX17" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="EY17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="EZ17" t="inlineStr">
-        <is>
-          <t>Embora a organização ofereça trilhas de aprendizagem e utilize o PDPI, a evidência apresentada não demonstra formalmente a existência de mecanismos institucionais de incentivo à participação. Falta a comprovação de políticas de estímulo, campanhas ou orientações ativas que encorajem os servidores a aderir às capacitações previstas.</t>
-        </is>
-      </c>
-      <c r="FA17" t="inlineStr">
-        <is>
-          <t>incentiva seus colaboradores e gestores a participar das ações de capacitação existentes</t>
         </is>
       </c>
       <c r="FB17" t="inlineStr">
@@ -6826,26 +6606,6 @@
           <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
         </is>
       </c>
-      <c r="FR33" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="FS33" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="FT33" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que, embora o plano mencione a participação de representante da alta administração no Comitê Permanente, não foi apresentado ato administrativo, despacho, portaria ou termo de assinatura que demonstre a aprovação formal do documento pela autoridade competente ou pelo colegiado da alta administração.</t>
-        </is>
-      </c>
-      <c r="FU33" t="inlineStr">
-        <is>
-          <t>o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8296,26 +8056,6 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
-      <c r="BV43" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BW43" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BX43" t="inlineStr">
-        <is>
-          <t>Não foi possível verificar a consideração de outros instrumentos de planejamento na elaboração do Plano de Contratações Anual. A ausência do documento de PCA impede qualquer análise sobre sua integração com o planejamento organizacional. A evidência é insuficiente para a verificação do critério. Falta a apresentação do documento de planejamento de contratações para aferir sua conformidade com os demais instrumentos institucionais.</t>
-        </is>
-      </c>
-      <c r="BY43" t="inlineStr">
-        <is>
-          <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
-        </is>
-      </c>
       <c r="CD43" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -8454,26 +8194,6 @@
       <c r="FU43" t="inlineStr">
         <is>
           <t>o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
-        </is>
-      </c>
-      <c r="FV43" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="FW43" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="FX43" t="inlineStr">
-        <is>
-          <t>O plano não demonstra o vínculo com a proposta orçamentária da área de TI ou com o plano de contratações. O documento lista prioridades na página 4, mas não vincula tais itens aos instrumentos de planejamento orçamentário ou de contratações da organização. A evidência é insuficiente por não estabelecer a fundamentação orçamentária e contratual requerida.</t>
-        </is>
-      </c>
-      <c r="FY43" t="inlineStr">
-        <is>
-          <t>o plano de TI fundamenta a proposta orçamentária da área de TI e o plano de contratações</t>
         </is>
       </c>
       <c r="HB43" t="inlineStr">
@@ -9024,26 +8744,6 @@
           <t>incentiva seus colaboradores e gestores a participar das ações de capacitação existentes</t>
         </is>
       </c>
-      <c r="FN47" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="FO47" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="FP47" t="inlineStr">
-        <is>
-          <t>A evidência apresentada é insuficiente para comprovar a existência de uma área de tecnologia da informação ou a atribuição formal de cargos e funções nesta área na estrutura organizacional da Prefeitura de Japeri. O documento encaminhado consiste em um glossário de termos genéricos aplicáveis à governança e gestão de tecnologia, sem qualquer vínculo com a estrutura ou atos normativos do auditado. A suficiência da evidência é nula, visto que não traz elementos capazes de atestar a organização interna da TI no ente. Permanece a lacuna quanto à ausência de documentos comprobatórios institucionais, como leis, decretos, regimentos internos ou organogramas que formalizem a estrutura de TI no quadro de pessoal do auditado.</t>
-        </is>
-      </c>
-      <c r="FQ47" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos ou funções formalmente atribuídas à área de tecnologia da informação</t>
-        </is>
-      </c>
       <c r="HZ47" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -9171,6 +8871,26 @@
           <t>as responsabilidades e atribuições dos gestores da área de tecnologia da informação estão definidas, documentadas e publicadas</t>
         </is>
       </c>
+      <c r="BV48" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="BW48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BX48" t="inlineStr">
+        <is>
+          <t>A integração do PCA com outros instrumentos de planejamento não está demonstrada. Embora a organização possua um PEDTIC, a documentação não apresenta o vínculo explícito ou a menção de como outros instrumentos de planejamento (como PPA, LDO ou LOA) foram considerados durante a elaboração e atualização do PCA. A evidência é insuficiente por omitir a demonstração dessa articulação.</t>
+        </is>
+      </c>
+      <c r="BY48" t="inlineStr">
+        <is>
+          <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
       <c r="CL48" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -10006,86 +9726,6 @@
           <t>MPERJ</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que o item não foi atendido, visto que não foram apresentados os documentos de ANS pactuados. Sem esses registros, não é possível verificar a compatibilidade das informações contidas no catálogo com as metas negociadas. A evidência apresentada é insuficiente para validar a atualização e a compatibilidade do catálogo.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>o catálogo está atualizado e as informações que nele constam são compatíveis com os Acordos de Níveis de Serviço (ANS) estabelecidos pela área de tecnologia da informação e as áreas de negócio da organização</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que o item não foi atendido, uma vez que não foi comprovado o acesso efetivo ao catálogo pelos usuários. A planilha indica uma coluna de visibilidade, mas não houve a apresentação de prints do portal de serviços ou outro meio de comprovação de disponibilidade. A evidência é insuficiente para atestar o fácil acesso.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>o catálogo é de fácil acesso e está amplamente disponível a seus usuários e às equipes de suporte</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que o item não foi atendido, dado que não constam nos autos documentos de ANS formalizados. A planilha enviada não constitui um acordo firmado entre a área de TI e as áreas de negócio. A evidência é insuficiente para a comprovação da pactuação de níveis de serviço.</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>são formalizados ANS contendo metas de nível de serviço acordadas com representantes das áreas de negócio clientes</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que o item não foi atendido, pois não foram disponibilizados relatórios, dashboards ou métricas de desempenho. A imagem fornecida é um chamado de teste e não reflete a rotina de monitoramento de níveis de serviço. A evidência apresentada é insuficiente para comprovar o monitoramento contínuo.</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>a área de gestão de tecnologia da informação monitora continuamente o alcance dos níveis de serviço estabelecidos nos ANS</t>
-        </is>
-      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -10106,26 +9746,6 @@
           <t>a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes</t>
         </is>
       </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>A existência de uma base de dados consolidada e atualizada com configurações e relacionamentos entre ativos e serviços não foi demonstrada pela evidência enviada. Embora a Resolução GPGJ nº 2.785 mencione a responsabilidade de controle, o documento não constitui o registro ou a base de dados em si. A evidência é insuficiente para atestar a conformidade, pois não apresenta o inventário, extratos ou relatórios estruturados. A lacuna identificada é a inexistência de documentação técnica ou acesso ao sistema que comprove a manutenção efetiva da base de configurações.</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
-        </is>
-      </c>
       <c r="AL53" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -10146,46 +9766,6 @@
           <t>a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças</t>
         </is>
       </c>
-      <c r="BR53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BS53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BT53" t="inlineStr">
-        <is>
-          <t>A avaliação indica que a evidência enviada refere-se exclusivamente à prestação de serviços de nuvem, sem contemplar o inventário ou controle de softwares instalados nos dispositivos da rede interna da organização. Não há comprovação de gestão de softwares para o parque tecnológico institucional. A evidência é insuficiente para a abrangência exigida pelo item.</t>
-        </is>
-      </c>
-      <c r="BU53" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
-        </is>
-      </c>
-      <c r="CH53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CI53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CJ53" t="inlineStr">
-        <is>
-          <t>A avaliação indica que o escopo do contrato apresentado limita-se aos serviços em nuvem (SERPRO Multicloud), não abrangendo o inventário ou o controle de dispositivos da rede interna da organização. Não foram apresentadas evidências documentais que demonstrem tal gerenciamento fora do ambiente cloud. A evidência é insuficiente por não cobrir o parque tecnológico da organização.</t>
-        </is>
-      </c>
-      <c r="CK53" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
-        </is>
-      </c>
       <c r="DZ53" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -10204,26 +9784,6 @@
       <c r="EC53" t="inlineStr">
         <is>
           <t>há base(s) de conhecimento que registra(m) erros conhecidos e problemas, de modo a tornar eficiente e efetiva a resolução de incidentes</t>
-        </is>
-      </c>
-      <c r="GT53" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="GU53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="GV53" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que o item não foi atendido, pois o catálogo apresentado carece de elementos essenciais exigidos. A evidência contém prazos de contrato, mas não descreve horários de suporte nem pontos de contato claros para as solicitações dos usuários. A análise da evidência indica que os dados são parciais e incompletos.</t>
-        </is>
-      </c>
-      <c r="GW53" t="inlineStr">
-        <is>
-          <t>o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes)</t>
         </is>
       </c>
     </row>
@@ -10300,26 +9860,6 @@
           <t>NOVA IGUAÇU</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que o item está não conforme. Embora o ato constitutivo tenha sido publicado em 14 de outubro de 2025 (p. 2-3), não foram apresentados elementos que comprovem o efetivo funcionamento do comitê até a presente data. A evidência limita-se ao decreto de criação, inexistindo atas de reunião, registros de deliberações ou a elaboração do regimento interno previsto no Art. 4º. O elemento faltante essencial é a comprovação da realização prática das atividades pelo comitê.</t>
-        </is>
-      </c>
-      <c r="BA55" t="inlineStr">
-        <is>
-          <t>o comitê de tecnologia da informação realiza as atividades previstas em ato constitutivo</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -11116,26 +10656,6 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
-      <c r="BJ63" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BK63" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BL63" t="inlineStr">
-        <is>
-          <t>A evidência apresentada é insuficiente para atender ao critério de cargo efetivo de tecnologia da informação. A Lei nº 2087/2021, enviada como comprovação, dispõe exclusivamente sobre a criação de cargos em comissão e funções gratificadas na estrutura administrativa municipal. Não foram localizados elementos que comprovem a existência de cargo de provimento permanente, ou seja, de carreira, dedicado especificamente à área de TI. Persiste a lacuna quanto à demonstração documental de cargo efetivo para esta finalidade.</t>
-        </is>
-      </c>
-      <c r="BM63" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos efetivos em tecnologia da informação</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -11163,6 +10683,26 @@
           <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
         </is>
       </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia que o requisito não está atendido. Não há elementos na evidência que vinculem o PCA à proposta orçamentária do município. A evidência é insuficiente para atestar a fundamentação do orçamento a partir do PCA. Faltam evidências, como pareceres ou memórias de cálculo, que demonstrem a utilização do plano no embasamento orçamentário.</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>o PCA fundamenta a proposta orçamentária da organização</t>
+        </is>
+      </c>
       <c r="BF64" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -11181,6 +10721,26 @@
       <c r="BI64" t="inlineStr">
         <is>
           <t>as responsabilidades e atribuições dos gestores da área de tecnologia da informação estão definidas, documentadas e publicadas</t>
+        </is>
+      </c>
+      <c r="BV64" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="BW64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BX64" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia que o requisito não está atendido. O documento apresentado não evidencia a conexão do PCA com outros instrumentos de planejamento institucional, tais como PPA, LDO ou LOA. A evidência é insuficiente para demonstrar o alinhamento com outros instrumentos de gestão. Falta documentação que comprove a integração metodológica entre o PCA e os planos orçamentários da organização.</t>
+        </is>
+      </c>
+      <c r="BY64" t="inlineStr">
+        <is>
+          <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
         </is>
       </c>
       <c r="CD64" t="inlineStr">
@@ -11370,44 +10930,24 @@
           <t>o catálogo está atualizado e as informações que nele constam são compatíveis com os Acordos de Níveis de Serviço (ANS) estabelecidos pela área de tecnologia da informação e as áreas de negócio da organização</t>
         </is>
       </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que não há evidência suficiente para comprovar a existência de uma base de dados consolidada e atualizada. O diagrama de topologia constitui apenas uma representação visual estática, sem metadados, datas de atualização ou registros que permitam verificar a abrangência e a consistência da base de ativos e seus relacionamentos. O material enviado não supre a necessidade de evidenciar a manutenção de um repositório formal de configurações.</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
-        </is>
-      </c>
-      <c r="AL65" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que não há evidência de que a base de configurações seja utilizada no processo de gestão de mudanças. O diagrama fornecido não apresenta vínculos, registros ou fluxos que associem os ativos mapeados a solicitações de mudança, análises de impacto ou acompanhamento de alterações na infraestrutura. A ausência de elementos que integrem a base de dados ao processo de mudanças impede a conformidade com o critério.</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças</t>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria não encontrou evidências que demonstrem a correlação entre o PCA e a proposta orçamentária. Embora o portal exiba o valor total estimado, não há registro da fundamentação orçamentária decorrente deste plano. Ausência de documento, nota técnica ou memória de cálculo que vincule o PCA à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>o PCA fundamenta a proposta orçamentária da organização</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -11450,6 +10990,26 @@
           <t>possui em sua estrutura cargos efetivos em tecnologia da informação</t>
         </is>
       </c>
+      <c r="BV65" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="BW65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BX65" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria não identificou elementos que conectem o PCA aos demais instrumentos de planejamento institucional, tais como PPA, LDO ou plano estratégico. A evidência restringe-se aos dados disponibilizados no portal nacional, sem demonstrar o alinhamento ou integração com outros instrumentos. Ausência de comprovação documental da integração do PCA com o planejamento institucional.</t>
+        </is>
+      </c>
+      <c r="BY65" t="inlineStr">
+        <is>
+          <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
       <c r="CL65" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -11650,26 +11210,6 @@
           <t>define os papéis e responsabilidades da área de gestão de tecnologia da informação</t>
         </is>
       </c>
-      <c r="DZ65" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="EA65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="EB65" t="inlineStr">
-        <is>
-          <t>Não foram apresentadas evidências que comprovem a existência ou a utilização de uma base de conhecimento para registro de erros conhecidos e problemas recorrentes. Embora a política preveja o registro de incidentes, não há evidência de repositório, catálogo ou sistema de 'conhecimento' (KEDB) que auxilie a equipe na resolução eficiente de problemas. A ausência de evidência documental específica torna o item não conforme.</t>
-        </is>
-      </c>
-      <c r="EC65" t="inlineStr">
-        <is>
-          <t>há base(s) de conhecimento que registra(m) erros conhecidos e problemas, de modo a tornar eficiente e efetiva a resolução de incidentes</t>
-        </is>
-      </c>
       <c r="ET65" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -11690,26 +11230,6 @@
           <t>os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado</t>
         </is>
       </c>
-      <c r="FR65" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="FS65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="FT65" t="inlineStr">
-        <is>
-          <t>A evidência apresentada é insuficiente para demonstrar o atendimento ao critério. Embora o plano cite a criação do Comitê PEDTIC por meio da Portaria nº 505/2023, não foi apresentado ato formal, despacho ou documento assinado que comprove a aprovação final do plano pelo dirigente máximo ou por colegiado da alta administração. Ausência de evidência documental da aprovação oficial do PEDTIC 2024.</t>
-        </is>
-      </c>
-      <c r="FU65" t="inlineStr">
-        <is>
-          <t>o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
-        </is>
-      </c>
       <c r="GH65" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -11748,26 +11268,6 @@
       <c r="GO65" t="inlineStr">
         <is>
           <t>rotinas de monitoramento do desempenho da gestão de tecnologia da informação estão definidas</t>
-        </is>
-      </c>
-      <c r="GT65" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="GU65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="GV65" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que o item não foi atendido. Não foram apresentadas evidências documentais ou de sistemas que detalhem metas definidas para cada serviço, como prazos, horários de atendimento ou pontos de contato. A imagem do dashboard operacional apresentado não contém as informações de catálogo solicitadas. A evidência é insuficiente pela ausência de documento do catálogo de serviços detalhando os parâmetros estabelecidos.</t>
-        </is>
-      </c>
-      <c r="GW65" t="inlineStr">
-        <is>
-          <t>o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes)</t>
         </is>
       </c>
     </row>
@@ -12780,46 +12280,6 @@
           <t>SEDEC</t>
         </is>
       </c>
-      <c r="BR75" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BS75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BT75" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia como não conforme, pois a evidência restringe-se ao texto do regulamento, que delega a responsabilidade pela gestão de softwares e licenças. Não foram apresentados os inventários de softwares instalados ou relatórios de controle de licenciamento. A lacuna consiste na ausência de registros que evidenciem a operação prática da gestão de softwares na rede.</t>
-        </is>
-      </c>
-      <c r="BU75" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
-        </is>
-      </c>
-      <c r="CH75" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CI75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CJ75" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia como não conforme, uma vez que apenas foi apresentada a competência regimental da Coordenação de Infraestrutura e Suporte para gerenciar ativos. Não foram disponibilizados o inventário físico ou lógico dos dispositivos, nem registros de sua manutenção e controle. A documentação apresentada é suficiente para demonstrar a estrutura organizacional, mas insuficiente para comprovar a execução efetiva do controle de ativos.</t>
-        </is>
-      </c>
-      <c r="CK75" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
-        </is>
-      </c>
       <c r="GX75" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -14724,26 +14184,6 @@
           <t>a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Embora a norma defina a responsabilidade pela comunicação e ações emergenciais, faltam as diretrizes detalhadas de escalamento. Não há definição de níveis, gatilhos, prazos ou fluxos formais de escalamento exigidos para o tratamento de incidentes. A evidência é insuficiente por omitir procedimentos operacionais padronizados de escalonamento.</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa</t>
-        </is>
-      </c>
       <c r="Z87" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -14862,26 +14302,6 @@
       <c r="BE87" t="inlineStr">
         <is>
           <t>estabeleceu objetivos, indicadores e metas para a gestão de tecnologia da informação</t>
-        </is>
-      </c>
-      <c r="BN87" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BO87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BP87" t="inlineStr">
-        <is>
-          <t>A norma interna estabelece a obrigatoriedade da classificação de gravidade e impacto, mas não apresenta as regras, matrizes ou critérios objetivos de priorização e escalonamento. A ausência de definição de fluxo de escalonamento e níveis de severidade torna a evidência insuficiente. Falta documentação procedimental que detalhe o rito operacional para priorização e escalonamento.</t>
-        </is>
-      </c>
-      <c r="BQ87" t="inlineStr">
-        <is>
-          <t>definiu regras para a priorização e o escalamento de incidentes</t>
         </is>
       </c>
       <c r="BR87" t="inlineStr">
@@ -15271,46 +14691,6 @@
           <t>a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>O documento não define procedimentos ou responsabilidades quanto à notificação e tratamento de incidentes de segurança da informação. Embora existam cláusulas sobre sigilo e LGPD, não há diretrizes para ações emergenciais, escalamento ou comunicação específica para eventos de segurança. A evidência é insuficiente devido à ausência de fluxo ou norma de tratamento de incidentes de segurança.</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>Não constam no Acordo de Cooperação Técnica procedimentos para análise de incidentes, identificação de causas raízes ou implementação de ações corretivas. O instrumento menciona apenas a "análise dos resultados" do acordo ao fim da vigência, sem relação com a gestão de incidentes de TI ou segurança. A evidência é insuficiente por ausência de metodologia ou registros de análise pós-incidente.</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>definiu procedimentos e responsabilidades quanto à análise dos incidentes, identificação de causas raízes e planejamento e implementação de ações corretivas</t>
-        </is>
-      </c>
       <c r="AD88" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -15331,46 +14711,6 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
-      <c r="BN88" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BO88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BP88" t="inlineStr">
-        <is>
-          <t>Não há, no Acordo de Cooperação Técnica, regras ou critérios definidos para a priorização e escalamento de incidentes. O documento limita-se a estabelecer responsabilidades genéricas pela coordenação da parceria e suporte técnico. A evidência é insuficiente, pois faltam matrizes de impacto, severidade ou fluxos operacionais de escalonamento.</t>
-        </is>
-      </c>
-      <c r="BQ88" t="inlineStr">
-        <is>
-          <t>definiu regras para a priorização e o escalamento de incidentes</t>
-        </is>
-      </c>
-      <c r="CD88" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CE88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CF88" t="inlineStr">
-        <is>
-          <t>O Acordo de Cooperação Técnica não constitui a formalização requerida para o processo de gestão de incidentes. Não foi apresentada norma interna, guia ou procedimento específico que defina etapas, papéis e responsabilidades para o tratamento de incidentes. A evidência é insuficiente por não apresentar o instrumento normativo do processo.</t>
-        </is>
-      </c>
-      <c r="CG88" t="inlineStr">
-        <is>
-          <t>o(s) processo(s) de gestão de incidentes está(ão) formalizado(s) (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
-        </is>
-      </c>
       <c r="DB88" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -15409,26 +14749,6 @@
       <c r="DM88" t="inlineStr">
         <is>
           <t>são disponibilizados artefatos padronizados para a fase de seleção de fornecedores, como minutas, checklists, modelos de edital, pareceres, critérios de julgamento ou documentos equivalentes</t>
-        </is>
-      </c>
-      <c r="ED88" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="EE88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="EF88" t="inlineStr">
-        <is>
-          <t>O Decreto 48.209/2022 não apresenta ou remete a um inventário de ativos associados à informação da organização. O normativo disciplina o funcionamento e os usuários do sistema SEI-RJ, mas não fornece listagem, catálogo ou relação de ativos de hardware, software, dados ou documentos. É necessária a apresentação de inventário formal que contemple os ativos de informação corporativos.</t>
-        </is>
-      </c>
-      <c r="EG88" t="inlineStr">
-        <is>
-          <t>mantém um inventário dos ativos associados à informação</t>
         </is>
       </c>
       <c r="EH88" t="inlineStr">
@@ -16186,46 +15506,6 @@
           <t>o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes)</t>
         </is>
       </c>
-      <c r="HF93" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="HG93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="HH93" t="inlineStr">
-        <is>
-          <t>O item é considerado não conforme. O documento encaminhado possui caráter orientativo geral e não contém registros que comprovem a participação efetiva das áreas demandantes da organização no processo de planejamento de TI. É necessária a apresentação de evidências documentais internas, como atas de reuniões, fluxos de trabalho ou registros de oficialização de demanda.</t>
-        </is>
-      </c>
-      <c r="HI93" t="inlineStr">
-        <is>
-          <t>as áreas demandantes de soluções de TI participam do processo de planejamento de tecnologia da informação</t>
-        </is>
-      </c>
-      <c r="HN93" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="HO93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="HP93" t="inlineStr">
-        <is>
-          <t>O item é considerado não conforme. Não foram apresentadas evidências documentais produzidas pelo auditado que demonstrem a realização de análises de benefícios, custos e riscos para subsidiar a seleção e priorização de iniciativas de TI. A documentação fornecida refere-se apenas a orientações externas e não substitui os estudos técnicos ou registros de decisão internos necessários.</t>
-        </is>
-      </c>
-      <c r="HQ93" t="inlineStr">
-        <is>
-          <t>as análises de benefícios, de custos e de riscos subsidiam as decisões relacionadas à seleção e à priorização das iniciativas de TI (projetos e ações)</t>
-        </is>
-      </c>
       <c r="HV93" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -16253,26 +15533,6 @@
           <t>TCE-RJ</t>
         </is>
       </c>
-      <c r="BJ94" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BK94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BL94" t="inlineStr">
-        <is>
-          <t>A evidência apresentada é insuficiente para comprovar a existência de cargos efetivos de tecnologia da informação. Embora a Resolução n° 471/2026 defina a estrutura organizacional do órgão, o seu anexo detalha apenas a ocupação de cargos em comissão (CCDAL) e funções de confiança (DAI), sem mencionar a existência de carreiras ou cargos de provimento efetivo de TI. A lacuna consiste na ausência de normativo ou documento que discrimine a criação de cargos efetivos voltados a essa área.</t>
-        </is>
-      </c>
-      <c r="BM94" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos efetivos em tecnologia da informação</t>
-        </is>
-      </c>
       <c r="CT94" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -16787,66 +16047,6 @@
           <t>são formalizados ANS contendo metas de nível de serviço acordadas com representantes das áreas de negócio clientes</t>
         </is>
       </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>A evidência apresentada é insuficiente para demonstrar o cumprimento do requisito de análise prévia e aprovação técnica das contratações de TI. O arquivo disponibilizado consiste, exclusivamente, na captura de tela de uma ferramenta de compartilhamento de arquivos, sem qualquer teor normativo ou registro administrativo que comprove o fluxo de governança exigido. A avaliação realizada constata a ausência de elementos que comprovem a existência ou a aplicação da rotina de aprovação técnica pela área de gestão de TI. Faz-se necessária a apresentação de norma interna que estabeleça o fluxo obrigatório e de evidências de casos concretos que demonstrem a efetiva tramitação de contratações sob tal diretriz.</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
-        </is>
-      </c>
-      <c r="BJ96" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BK96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BL96" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que a evidência é insuficiente. O arquivo enviado apresenta apenas a interface de configuração de um serviço de compartilhamento de arquivos, sem conter o ato normativo, edital ou documento estrutural que comprove a existência de cargo efetivo de tecnologia da informação. A evidência não permite verificar a existência ou previsão de tais cargos no quadro de pessoal do auditado. A lacuna consiste na ausência de documento comprobatório formal.</t>
-        </is>
-      </c>
-      <c r="BM96" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos efetivos em tecnologia da informação</t>
-        </is>
-      </c>
-      <c r="CT96" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CU96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CV96" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica a insuficiência da prova documental. A evidência fornecida restringe-se a uma interface digital de compartilhamento, sem apresentar lei, edital, plano de cargos ou documento congênere que demonstre a criação ou previsão de cargos efetivos de segurança da informação. A ausência de conteúdo substantivo impede a verificação do item. A lacuna reside na falta de documento formal que sustente a existência do referido cargo.</t>
-        </is>
-      </c>
-      <c r="CW96" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos efetivos em segurança da informação</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -16939,26 +16139,6 @@
       <c r="AG98" t="inlineStr">
         <is>
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que o requisito não foi atendido. A evidência apresentada é de natureza patrimonial e não comprova a manutenção de uma base de dados consolidada que registre as configurações dos serviços de TI e os relacionamentos entre eles. A evidência é insuficiente por não apresentar evidências de um sistema de gestão de configurações (CMDB) ou equivalente que permita o rastreamento dos ativos de TI e suas interdependências. Falta comprovação de existência, atualização e uso de uma base de dados de configuração voltada especificamente para serviços de TI.</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr">

--- a/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
@@ -1836,26 +1836,6 @@
           <t>AGERIO</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que a execução das atividades do comitê não foi comprovada. Embora a política liste as atribuições do ComTI (item 5.8.3), não foram apresentados registros, atas de reunião ou pareceres que materializem a efetiva atuação do órgão. Há lacuna de evidência sobre o funcionamento prático do comitê.</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>o comitê de tecnologia da informação realiza as atividades previstas em ato constitutivo</t>
-        </is>
-      </c>
       <c r="BB3" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -8176,26 +8156,6 @@
           <t>as lacunas de competências técnicas da área de tecnologia da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas</t>
         </is>
       </c>
-      <c r="FR43" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="FS43" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="FT43" t="inlineStr">
-        <is>
-          <t>Não consta evidência da aprovação formal do plano pelo dirigente máximo ou colegiado da alta administração. Embora o documento apresente um histórico de controle de versões na página 1, não há documento anexo, assinatura ou ato administrativo que comprove a autorização formal. A evidência é insuficiente por omitir a validação pela autoridade competente.</t>
-        </is>
-      </c>
-      <c r="FU43" t="inlineStr">
-        <is>
-          <t>o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
-        </is>
-      </c>
       <c r="HB43" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -9746,6 +9706,26 @@
           <t>a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes</t>
         </is>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>A existência de uma base de dados consolidada e atualizada com configurações e relacionamentos entre ativos e serviços não foi demonstrada pela evidência enviada. Embora a Resolução GPGJ nº 2.785 mencione a responsabilidade de controle, o documento não constitui o registro ou a base de dados em si. A evidência é insuficiente para atestar a conformidade, pois não apresenta o inventário, extratos ou relatórios estruturados. A lacuna identificada é a inexistência de documentação técnica ou acesso ao sistema que comprove a manutenção efetiva da base de configurações.</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
+        </is>
+      </c>
       <c r="AL53" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -12280,6 +12260,46 @@
           <t>SEDEC</t>
         </is>
       </c>
+      <c r="BR75" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="BS75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BT75" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia como não conforme, pois a evidência restringe-se ao texto do regulamento, que delega a responsabilidade pela gestão de softwares e licenças. Não foram apresentados os inventários de softwares instalados ou relatórios de controle de licenciamento. A lacuna consiste na ausência de registros que evidenciem a operação prática da gestão de softwares na rede.</t>
+        </is>
+      </c>
+      <c r="BU75" t="inlineStr">
+        <is>
+          <t>gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
+        </is>
+      </c>
+      <c r="CH75" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="CI75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="CJ75" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia como não conforme, uma vez que apenas foi apresentada a competência regimental da Coordenação de Infraestrutura e Suporte para gerenciar ativos. Não foram disponibilizados o inventário físico ou lógico dos dispositivos, nem registros de sua manutenção e controle. A documentação apresentada é suficiente para demonstrar a estrutura organizacional, mas insuficiente para comprovar a execução efetiva do controle de ativos.</t>
+        </is>
+      </c>
+      <c r="CK75" t="inlineStr">
+        <is>
+          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
+        </is>
+      </c>
       <c r="GX75" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -13796,46 +13816,6 @@
           <t>incentiva seus colaboradores e gestores a participar das ações de capacitação existentes</t>
         </is>
       </c>
-      <c r="GL83" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="GM83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="GN83" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica a não conformidade, pois não foram apresentados normas ou procedimentos internos da SEINFRA que definam rotinas de monitoramento da gestão de tecnologia. A documentação enviada limita-se a uma análise externa que destaca a inexistência de diversos quesitos obrigatórios do instrumento PEDTIC. Há lacuna relevante quanto à formalização de mecanismos internos de acompanhamento de desempenho, o que impede a validação desta rotina.</t>
-        </is>
-      </c>
-      <c r="GO83" t="inlineStr">
-        <is>
-          <t>rotinas de monitoramento do desempenho da gestão de tecnologia da informação estão definidas</t>
-        </is>
-      </c>
-      <c r="GP83" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="GQ83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="GR83" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica a não conformidade, uma vez que os indicadores apresentados referem-se à nota do instrumento avaliado pelo órgão externo e não representam métricas internas de desempenho da gestão de TIC coletadas e analisadas pela SEINFRA. A análise técnica do documento evidencia que diversos quesitos obrigatórios de medição, como status de metas e inventário de recursos, constam como inexistentes. A evidência é insuficiente para confirmar a implantação de um sistema de indicadores de desempenho com coleta e análise de dados internos.</t>
-        </is>
-      </c>
-      <c r="GS83" t="inlineStr">
-        <is>
-          <t>os indicadores de desempenho da gestão de tecnologia da informação estão implantados (há coleta e análise dos dados necessários à medição de desempenho)</t>
-        </is>
-      </c>
       <c r="HV83" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -14671,26 +14651,6 @@
           <t>a área de gestão de tecnologia da informação monitora continuamente o alcance dos níveis de serviço estabelecidos nos ANS</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>O documento não estabelece níveis de serviço (SLAs) nem acordos com áreas clientes para a resolução de incidentes. O texto trata apenas de cooperação institucional e disponibilização de infraestrutura, sem vincular a resolução de demandas a tempos-alvo ou metas de disponibilidade. A evidência apresentada é insuficiente para comprovar a existência de tais acordos.</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes</t>
-        </is>
-      </c>
       <c r="AD88" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -15366,26 +15326,6 @@
           <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
         </is>
       </c>
-      <c r="CH93" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CI93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CJ93" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que não foram apresentadas evidências documentais que comprovem a execução do controle. O documento apresentado restringe-se a registros de backup, não contendo inventário ou controle de dispositivos. Lacuna: inexistência de inventário de hardware ou de dispositivos de controle de rede.</t>
-        </is>
-      </c>
-      <c r="CK93" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
-        </is>
-      </c>
       <c r="CX93" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -16141,24 +16081,24 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
-      <c r="BJ98" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BK98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BL98" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que a evidência apresentada é insuficiente para comprovar a existência de cargos efetivos de tecnologia da informação. O auditado forneceu apenas uma declaração textual com link externo para o 'Manual de Cargos da UERJ', sem anexar o referido documento ao pacote probatório. O uso de referência externa não supre a necessidade de juntada da documentação oficial aos autos, impedindo a verificação formal do conteúdo alegado. Conclui-se pela insuficiência probatória, dada a ausência do documento comprobatório ou norma equivalente no pacote de evidências.</t>
-        </is>
-      </c>
-      <c r="BM98" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos efetivos em tecnologia da informação</t>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>A avaliação realizada indica que o requisito não foi atendido. A evidência apresentada é de natureza patrimonial e não comprova a manutenção de uma base de dados consolidada que registre as configurações dos serviços de TI e os relacionamentos entre eles. A evidência é insuficiente por não apresentar evidências de um sistema de gestão de configurações (CMDB) ou equivalente que permita o rastreamento dos ativos de TI e suas interdependências. Falta comprovação de existência, atualização e uso de uma base de dados de configuração voltada especificamente para serviços de TI.</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
         </is>
       </c>
       <c r="BV98" t="inlineStr">
@@ -16359,26 +16299,6 @@
       <c r="EC98" t="inlineStr">
         <is>
           <t>há base(s) de conhecimento que registra(m) erros conhecidos e problemas, de modo a tornar eficiente e efetiva a resolução de incidentes</t>
-        </is>
-      </c>
-      <c r="FN98" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="FO98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="FP98" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que a evidência apresentada é insuficiente para comprovar a existência de funções ou cargos atribuídos à área de tecnologia da informação. O auditado limitou-se a indicar um link externo para o 'Manual de Cargos da UERJ', sem incluir o documento nos arquivos enviados para análise. A referência externa não constitui meio de prova apto a fundamentar a conformidade, pois não permite a verificação direta do conteúdo pelo auditor. Identifica-se a necessidade de apresentação da documentação oficial pertinente ao pacote de evidências para o devido saneamento.</t>
-        </is>
-      </c>
-      <c r="FQ98" t="inlineStr">
-        <is>
-          <t>possui em sua estrutura cargos ou funções formalmente atribuídas à área de tecnologia da informação</t>
         </is>
       </c>
     </row>

--- a/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
@@ -2332,26 +2332,6 @@
           <t>CASIMIRO DE ABREU</t>
         </is>
       </c>
-      <c r="CX11" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CY11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CZ11" t="inlineStr">
-        <is>
-          <t>Apesar da alegação do auditado, a evidência documental apresentada não demonstra de forma clara e objetiva o fluxo, as responsabilidades ou os artefatos específicos para a gestão e fiscalização de contratos de TI. O documento carece de elementos verificáveis que comprovem o detalhamento dessas etapas.</t>
-        </is>
-      </c>
-      <c r="DA11" t="inlineStr">
-        <is>
-          <t>o processo de trabalho para a gestão e fiscalização de contratos contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2406,26 +2386,6 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>A Portaria apresentada não faz qualquer menção à existência de um Comitê de Tecnologia da Informação ou à sua composição por representantes de áreas relevantes. A evidência é insuficiente devido à ausência de ato constitutivo ou referência a instâncias colegiadas de governança de TI.</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>dispõe de comitê de tecnologia da informação composto por representantes de áreas relevantes da organização</t>
-        </is>
-      </c>
       <c r="BJ13" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -2947,26 +2907,6 @@
           <t>são disponibilizados artefatos padronizados para a gestão e fiscalização de contratos de TI, como modelos de plano de fiscalização, termos de recebimento, relatórios de acompanhamento, registros de ocorrências, avaliações de desempenho contratual ou documentos equivalentes</t>
         </is>
       </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>A evidência apresentada não configura um inventário de ativos, tratando-se apenas de visualização de volumes de armazenamento em rede. É necessário apresentar documento atualizado que relacione e descreva os ativos sob gestão da organização.</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>mantém um inventário dos ativos associados à informação</t>
-        </is>
-      </c>
       <c r="EH16" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -7682,26 +7622,6 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia que o item não está conforme. O inventário contido nas páginas 22 a 51 lista equipamentos e softwares isoladamente, sem apresentar base de dados consolidada de configurações dos serviços de TI. A evidência falha ao não demonstrar o mapeamento de relacionamentos ou dependências entre infraestrutura, sistemas e serviços. A principal lacuna é a ausência de uma base de dados de gerenciamento de configuração (CMDB) efetiva e atualizada.</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
-        </is>
-      </c>
       <c r="AL41" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -7720,46 +7640,6 @@
       <c r="AO41" t="inlineStr">
         <is>
           <t>a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças</t>
-        </is>
-      </c>
-      <c r="BR41" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BS41" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BT41" t="inlineStr">
-        <is>
-          <t>Embora a norma estabeleça diretrizes sobre softwares autorizados, não foram apresentados listagens, registros de licenciamento ou evidências da gestão atual do parque de softwares. A evidência carece de dados operacionais que comprovem a execução do controle. Falta inventário de softwares instalados.</t>
-        </is>
-      </c>
-      <c r="BU41" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
-        </is>
-      </c>
-      <c r="CH41" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CI41" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CJ41" t="inlineStr">
-        <is>
-          <t>O normativo descreve a responsabilidade pelo controle de equipamentos, porém não apresenta o inventário atualizado ou registros que comprovem a execução do controle de dispositivos conectados à rede. A evidência é insuficiente por não conter o registro prático do inventário. Falta inventário de dispositivos atualizado.</t>
-        </is>
-      </c>
-      <c r="CK41" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
         </is>
       </c>
       <c r="CL41" t="inlineStr">
@@ -8036,6 +7916,26 @@
           <t>as contratações de soluções de TI, independentemente de qual seja a área demandante, são obrigatoriamente submetidas à análise prévia e aprovação técnica da área de gestão de TI</t>
         </is>
       </c>
+      <c r="BV43" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="BW43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BX43" t="inlineStr">
+        <is>
+          <t>Não foi possível verificar a consideração de outros instrumentos de planejamento na elaboração do Plano de Contratações Anual. A ausência do documento de PCA impede qualquer análise sobre sua integração com o planejamento organizacional. A evidência é insuficiente para a verificação do critério. Falta a apresentação do documento de planejamento de contratações para aferir sua conformidade com os demais instrumentos institucionais.</t>
+        </is>
+      </c>
+      <c r="BY43" t="inlineStr">
+        <is>
+          <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
       <c r="CD43" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -8154,6 +8054,26 @@
       <c r="FI43" t="inlineStr">
         <is>
           <t>as lacunas de competências técnicas da área de tecnologia da informação necessárias para a atuação dos colaboradores da organização são identificadas e documentadas</t>
+        </is>
+      </c>
+      <c r="FR43" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="FS43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="FT43" t="inlineStr">
+        <is>
+          <t>Não consta evidência da aprovação formal do plano pelo dirigente máximo ou colegiado da alta administração. Embora o documento apresente um histórico de controle de versões na página 1, não há documento anexo, assinatura ou ato administrativo que comprove a autorização formal. A evidência é insuficiente por omitir a validação pela autoridade competente.</t>
+        </is>
+      </c>
+      <c r="FU43" t="inlineStr">
+        <is>
+          <t>o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
         </is>
       </c>
       <c r="HB43" t="inlineStr">
@@ -10910,6 +10830,26 @@
           <t>o catálogo está atualizado e as informações que nele constam são compatíveis com os Acordos de Níveis de Serviço (ANS) estabelecidos pela área de tecnologia da informação e as áreas de negócio da organização</t>
         </is>
       </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>A avaliação realizada indica que não há evidência de que a base de configurações seja utilizada no processo de gestão de mudanças. O diagrama fornecido não apresenta vínculos, registros ou fluxos que associem os ativos mapeados a solicitações de mudança, análises de impacto ou acompanhamento de alterações na infraestrutura. A ausência de elementos que integrem a base de dados ao processo de mudanças impede a conformidade com o critério.</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças</t>
+        </is>
+      </c>
       <c r="AP65" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -11210,6 +11150,26 @@
           <t>os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado</t>
         </is>
       </c>
+      <c r="FR65" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="FS65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="FT65" t="inlineStr">
+        <is>
+          <t>A evidência apresentada é insuficiente para demonstrar o atendimento ao critério. Embora o plano cite a criação do Comitê PEDTIC por meio da Portaria nº 505/2023, não foi apresentado ato formal, despacho ou documento assinado que comprove a aprovação final do plano pelo dirigente máximo ou por colegiado da alta administração. Ausência de evidência documental da aprovação oficial do PEDTIC 2024.</t>
+        </is>
+      </c>
+      <c r="FU65" t="inlineStr">
+        <is>
+          <t>o plano de tecnologia da informação (plano de TI) é aprovado pelo dirigente máximo da organização ou por dirigente ou colegiado que integra a alta administração</t>
+        </is>
+      </c>
       <c r="GH65" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -11228,26 +11188,6 @@
       <c r="GK65" t="inlineStr">
         <is>
           <t>possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação</t>
-        </is>
-      </c>
-      <c r="GL65" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="GM65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="GN65" t="inlineStr">
-        <is>
-          <t>A avaliação realizada indica que o item não foi atendido. Embora existam sistemas de coleta de dados em operação, não foram apresentados documentos normativos, manuais ou atos administrativos que definam formalmente as rotinas de monitoramento. A análise crítica aponta que capturas de tela isoladas são insuficientes para comprovar a existência de processos de trabalho estabelecidos. A lacuna reside na ausência de normatização formal dos procedimentos de acompanhamento.</t>
-        </is>
-      </c>
-      <c r="GO65" t="inlineStr">
-        <is>
-          <t>rotinas de monitoramento do desempenho da gestão de tecnologia da informação estão definidas</t>
         </is>
       </c>
     </row>
@@ -12260,46 +12200,6 @@
           <t>SEDEC</t>
         </is>
       </c>
-      <c r="BR75" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="BS75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="BT75" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia como não conforme, pois a evidência restringe-se ao texto do regulamento, que delega a responsabilidade pela gestão de softwares e licenças. Não foram apresentados os inventários de softwares instalados ou relatórios de controle de licenciamento. A lacuna consiste na ausência de registros que evidenciem a operação prática da gestão de softwares na rede.</t>
-        </is>
-      </c>
-      <c r="BU75" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
-        </is>
-      </c>
-      <c r="CH75" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CI75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CJ75" t="inlineStr">
-        <is>
-          <t>A Equipe de Auditoria avalia como não conforme, uma vez que apenas foi apresentada a competência regimental da Coordenação de Infraestrutura e Suporte para gerenciar ativos. Não foram disponibilizados o inventário físico ou lógico dos dispositivos, nem registros de sua manutenção e controle. A documentação apresentada é suficiente para demonstrar a estrutura organizacional, mas insuficiente para comprovar a execução efetiva do controle de ativos.</t>
-        </is>
-      </c>
-      <c r="CK75" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
-        </is>
-      </c>
       <c r="GX75" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -13756,26 +13656,6 @@
           <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
         </is>
       </c>
-      <c r="CH83" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="CI83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="CJ83" t="inlineStr">
-        <is>
-          <t>Não foram apresentadas evidências de inventário ou controle de dispositivos conectados à rede. O documento enviado restringe-se a uma solicitação administrativa de backup e não trata da gestão ou inventário de ativos. Falta documentação técnica que comprove a existência de inventário e controle de dispositivos.</t>
-        </is>
-      </c>
-      <c r="CK83" t="inlineStr">
-        <is>
-          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
-        </is>
-      </c>
       <c r="EL83" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -13814,6 +13694,26 @@
       <c r="FA83" t="inlineStr">
         <is>
           <t>incentiva seus colaboradores e gestores a participar das ações de capacitação existentes</t>
+        </is>
+      </c>
+      <c r="GP83" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="GQ83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="GR83" t="inlineStr">
+        <is>
+          <t>A avaliação realizada indica a não conformidade, uma vez que os indicadores apresentados referem-se à nota do instrumento avaliado pelo órgão externo e não representam métricas internas de desempenho da gestão de TIC coletadas e analisadas pela SEINFRA. A análise técnica do documento evidencia que diversos quesitos obrigatórios de medição, como status de metas e inventário de recursos, constam como inexistentes. A evidência é insuficiente para confirmar a implantação de um sistema de indicadores de desempenho com coleta e análise de dados internos.</t>
+        </is>
+      </c>
+      <c r="GS83" t="inlineStr">
+        <is>
+          <t>os indicadores de desempenho da gestão de tecnologia da informação estão implantados (há coleta e análise dos dados necessários à medição de desempenho)</t>
         </is>
       </c>
       <c r="HV83" t="inlineStr">
@@ -14164,6 +14064,26 @@
           <t>a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes</t>
         </is>
       </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Embora a norma defina a responsabilidade pela comunicação e ações emergenciais, faltam as diretrizes detalhadas de escalamento. Não há definição de níveis, gatilhos, prazos ou fluxos formais de escalamento exigidos para o tratamento de incidentes. A evidência é insuficiente por omitir procedimentos operacionais padronizados de escalonamento.</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>definiu procedimentos e responsabilidades quanto à notificação e ao tratamento das notificações de incidentes de segurança da informação, bem como quanto à adoção de ações emergenciais, diretrizes para escalamento e comunicação interna e externa</t>
+        </is>
+      </c>
       <c r="Z87" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -14282,6 +14202,26 @@
       <c r="BE87" t="inlineStr">
         <is>
           <t>estabeleceu objetivos, indicadores e metas para a gestão de tecnologia da informação</t>
+        </is>
+      </c>
+      <c r="BN87" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="BO87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BP87" t="inlineStr">
+        <is>
+          <t>A norma interna estabelece a obrigatoriedade da classificação de gravidade e impacto, mas não apresenta as regras, matrizes ou critérios objetivos de priorização e escalonamento. A ausência de definição de fluxo de escalonamento e níveis de severidade torna a evidência insuficiente. Falta documentação procedimental que detalhe o rito operacional para priorização e escalonamento.</t>
+        </is>
+      </c>
+      <c r="BQ87" t="inlineStr">
+        <is>
+          <t>definiu regras para a priorização e o escalamento de incidentes</t>
         </is>
       </c>
       <c r="BR87" t="inlineStr">
@@ -14651,6 +14591,26 @@
           <t>a área de gestão de tecnologia da informação monitora continuamente o alcance dos níveis de serviço estabelecidos nos ANS</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>O documento não estabelece níveis de serviço (SLAs) nem acordos com áreas clientes para a resolução de incidentes. O texto trata apenas de cooperação institucional e disponibilização de infraestrutura, sem vincular a resolução de demandas a tempos-alvo ou metas de disponibilidade. A evidência apresentada é insuficiente para comprovar a existência de tais acordos.</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>a resolução de incidentes considera os níveis de serviços especificados em acordos com as áreas clientes</t>
+        </is>
+      </c>
       <c r="AD88" t="inlineStr">
         <is>
           <t>Não conforme</t>
@@ -15324,6 +15284,26 @@
       <c r="BY93" t="inlineStr">
         <is>
           <t>na elaboração do PCA são considerados os demais instrumentos de planejamento da organização</t>
+        </is>
+      </c>
+      <c r="CH93" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="CI93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="CJ93" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia que não foram apresentadas evidências documentais que comprovem a execução do controle. O documento apresentado restringe-se a registros de backup, não contendo inventário ou controle de dispositivos. Lacuna: inexistência de inventário de hardware ou de dispositivos de controle de rede.</t>
+        </is>
+      </c>
+      <c r="CK93" t="inlineStr">
+        <is>
+          <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
         </is>
       </c>
       <c r="CX93" t="inlineStr">

--- a/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/fontes-auditoria-pos-comentarios/painel-avaliacao-evidencias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IC99"/>
+  <dimension ref="A1:IG99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,6 +1602,26 @@
           <t>q0103[D]__pratica</t>
         </is>
       </c>
+      <c r="ID1" t="inlineStr">
+        <is>
+          <t>q2801ext[B]</t>
+        </is>
+      </c>
+      <c r="IE1" t="inlineStr">
+        <is>
+          <t>q2801ext[B]__resposta_afirmada</t>
+        </is>
+      </c>
+      <c r="IF1" t="inlineStr">
+        <is>
+          <t>q2801ext[B]__justificativa</t>
+        </is>
+      </c>
+      <c r="IG1" t="inlineStr">
+        <is>
+          <t>q2801ext[B]__pratica</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2526,6 +2546,26 @@
           <t>os processos de trabalho e os artefatos padronizados estão aderentes às normas legais e infralegais que regem as contratações públicas</t>
         </is>
       </c>
+      <c r="ID13" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF13" t="inlineStr">
+        <is>
+          <t>A evidência não contém modelos, minutas ou qualquer artefato padronizado destinado ao planejamento de contratações de TI. Não há referência aos documentos essenciais para a instrução processual desta fase.</t>
+        </is>
+      </c>
+      <c r="IG13" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2753,6 +2793,26 @@
           <t>definiu responsabilidades pelos ativos associados à informação</t>
         </is>
       </c>
+      <c r="ID14" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF14" t="inlineStr">
+        <is>
+          <t>Os artefatos disponibilizados, como modelos de Termo de Referência e Matriz de Riscos, possuem caráter genérico e não abrangem as particularidades exigidas para o planejamento de soluções de TI. Ausência de artefatos específicos para a especificação de requisitos de tecnologia, como software e hardware. A documentação apresentada não supre a necessidade de modelos voltados para TI.</t>
+        </is>
+      </c>
+      <c r="IG14" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3314,6 +3374,26 @@
           <t>possui em sua estrutura cargos ou funções formalmente atribuídas à área de tecnologia da informação</t>
         </is>
       </c>
+      <c r="ID17" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF17" t="inlineStr">
+        <is>
+          <t>Embora a imagem liste documentos preenchidos em uma contratação específica, isso não comprova a disponibilização de uma biblioteca de artefatos padronizados ou modelos para uso organizacional. A evidência falha em demonstrar a existência de templates ou modelos de referência padronizados.</t>
+        </is>
+      </c>
+      <c r="IG17" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5958,6 +6038,26 @@
           <t>as análises de benefícios, de custos e de riscos subsidiam as decisões relacionadas à seleção e à priorização das iniciativas de TI (projetos e ações)</t>
         </is>
       </c>
+      <c r="ID29" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF29" t="inlineStr">
+        <is>
+          <t>Não foram apresentados artefatos padronizados referentes à fase de planejamento, como DFD, ETP ou TR. A documentação enviada limitou-se a uma listagem de processos, sem conter modelos ou templates de trabalho. Faz-se necessária a disponibilização de exemplares ou modelos de artefatos adotados.</t>
+        </is>
+      </c>
+      <c r="IG29" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6459,6 +6559,26 @@
           <t>as áreas demandantes de soluções de TI participam do processo de planejamento de tecnologia da informação</t>
         </is>
       </c>
+      <c r="ID32" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF32" t="inlineStr">
+        <is>
+          <t>Foram identificados artefatos como DFD, ETP e Termo de Referência, porém em um contexto de padronização administrativa geral. Não foi possível verificar a existência de modelos ou documentos padronizados próprios para a fase de planejamento de TI. A evidência é insuficiente por não apresentar especificidade para o objeto de TI.</t>
+        </is>
+      </c>
+      <c r="IG32" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6653,6 +6773,26 @@
           <t>o processo de trabalho para a seleção de fornecedores contempla as etapas, as responsabilidades dos atores envolvidos e os artefatos resultantes de cada etapa</t>
         </is>
       </c>
+      <c r="ID34" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF34" t="inlineStr">
+        <is>
+          <t>Não foram disponibilizados modelos ou templates institucionais para artefatos de planejamento, tais como DFD, ETP, ou Matriz de Riscos. A evidência enviada restringe-se a e-mails de solicitação de cotação e propostas de fornecedores, que não comprovem a padronização desses documentos pela instituição.</t>
+        </is>
+      </c>
+      <c r="IG34" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7074,6 +7214,26 @@
           <t>relacionou-se, no perfil profissional, além de requerimentos de ordem legal, um conjunto de competências e habilidades que os ocupantes dos cargos de gestão devem possuir</t>
         </is>
       </c>
+      <c r="ID37" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF37" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia que não há artefatos padronizados para a fase de planejamento. Os documentos anexados referem-se apenas a atos administrativos pontuais de designação e ajustes orçamentários, não apresentando modelos de DFD, ETP, TR ou Matriz de Riscos. A evidência é insuficiente por tratar de assunto distinto da fase de planejamento de contratações. Faltam modelos ou formulários padronizados para as etapas de planejamento de TI.</t>
+        </is>
+      </c>
+      <c r="IG37" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7401,6 +7561,26 @@
           <t>possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação</t>
         </is>
       </c>
+      <c r="ID38" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF38" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria conclui que o item não está conforme. Não foram disponibilizados modelos ou exemplos de artefatos padronizados, impossibilitando a verificação de sua existência. A evidência fornecida restringe-se a uma listagem de contratos, sem conter os documentos requisitados. Ausência dos artefatos padronizados de planejamento, como DFD, ETP ou TR.</t>
+        </is>
+      </c>
+      <c r="IG38" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7595,6 +7775,26 @@
           <t>gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
         </is>
       </c>
+      <c r="ID40" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF40" t="inlineStr">
+        <is>
+          <t>A análise crítica aponta que, apesar de o regulamento interno prever a necessidade de utilização de artefatos padronizados como DFD, ETP e TR, o documento não disponibiliza os modelos ou minutas-padrão efetivamente aplicáveis à fase de planejamento de TI. O próprio normativo determina que tais modelos devem ser instituídos por ordens de serviço ou instruções normativas futuras, as quais não constam nos documentos enviados. A evidência é insuficiente pois não apresenta os instrumentos padronizados concretos voltados à realidade do planejamento de TI.</t>
+        </is>
+      </c>
+      <c r="IG40" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7802,6 +8002,26 @@
           <t>relacionou-se, no perfil profissional, além de requerimentos de ordem legal, um conjunto de competências e habilidades que os ocupantes dos cargos de gestão devem possuir</t>
         </is>
       </c>
+      <c r="ID41" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF41" t="inlineStr">
+        <is>
+          <t>A avaliação realizada conclui que a apresentação de uma única instância de ETP não é suficiente para comprovar a disponibilização institucional de artefatos padronizados. Não foram fornecidos modelos, templates ou normativos que indiquem que tais artefatos são padronizados e disponibilizados para uso recorrente na organização. A lacuna principal reside na ausência de evidência da padronização sistêmica dos artefatos de planejamento.</t>
+        </is>
+      </c>
+      <c r="IG41" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8644,6 +8864,26 @@
           <t>a área de TI possui atribuições formalizadas relacionadas à governança, planejamento ou gestão de tecnologia da informação</t>
         </is>
       </c>
+      <c r="ID47" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF47" t="inlineStr">
+        <is>
+          <t>O documento enviado é um glossário de termos e não disponibiliza artefatos padronizados, tais como modelos, templates ou checklists da organização para a fase de planejamento das contratações. Não foram encontrados exemplos de Documento de Formalização da Demanda (DFD), Estudo Técnico Preliminar (ETP), Termo de Referência (TR) ou Matriz de Riscos que comprovem a padronização pela organização auditada. A evidência é insuficiente por tratar apenas de definições conceituais genéricas sem vinculação documental com a entidade.</t>
+        </is>
+      </c>
+      <c r="IG47" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9158,6 +9398,26 @@
           <t>o processo de gestão de configuração e ativos está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
         </is>
       </c>
+      <c r="ID49" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF49" t="inlineStr">
+        <is>
+          <t>Não foram disponibilizados artefatos padronizados para o planejamento de contratações de TI. Embora a norma crie unidades responsáveis por contratos, não apresenta os modelos ou documentos padronizados exigidos, como DFD, ETP, TR ou Matriz de Riscos. A evidência é insuficiente pois, apesar de citar atribuições de planejamento, não entrega os modelos necessários ao critério. Faltam os templates de documentos de planejamento específicos para a realidade tecnológica.</t>
+        </is>
+      </c>
+      <c r="IG49" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -11190,6 +11450,26 @@
           <t>possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação</t>
         </is>
       </c>
+      <c r="ID65" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF65" t="inlineStr">
+        <is>
+          <t>A avaliação indica que não são disponibilizados artefatos padronizados para a fase de planejamento. O documento enviado trata apenas de competências de fiscalização, não oferecendo modelos de DFD, ETP, TR ou Matriz de Riscos. A evidência é insuficiente por não conter tais documentos nem indicação de sua existência. A lacuna consiste na ausência de modelos padronizados para o planejamento de contratações de TI.</t>
+        </is>
+      </c>
+      <c r="IG65" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -11317,6 +11597,26 @@
           <t>o processo de gestão de configuração e ativos está formalizado (a organização instituiu norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades)</t>
         </is>
       </c>
+      <c r="ID66" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF66" t="inlineStr">
+        <is>
+          <t>A avaliação realizada indica que o item não está conforme, uma vez que não foram apresentados artefatos padronizados para o planejamento de contratações de TI. A evidência restringe-se a citar números de processos sem expor modelos, minutas ou exemplos de documentos como DFD, ETP, TR ou matriz de riscos. A falta de templates ou artefatos de planejamento inviabiliza a constatação da disponibilidade de ferramentas padronizadas.</t>
+        </is>
+      </c>
+      <c r="IG66" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11584,6 +11884,26 @@
           <t>as análises de benefícios, de custos e de riscos subsidiam as decisões relacionadas à seleção e à priorização das iniciativas de TI (projetos e ações)</t>
         </is>
       </c>
+      <c r="ID67" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF67" t="inlineStr">
+        <is>
+          <t>Não foram apresentados artefatos padronizados para a fase de planejamento. O documento enviado restringe-se a um macrofluxo, não contendo modelos, templates ou referências a artefatos como DFD, ETP, TR ou matrizes de risco. A ausência desses documentos impede a avaliação da padronização e da prática de planejamento. Falta a disponibilização de qualquer modelo ou instrumento padronizado para esta etapa.</t>
+        </is>
+      </c>
+      <c r="IG67" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13549,6 +13869,26 @@
           <t>os gestores são selecionados com base em perfil profissional previamente definido e documentado, e compatível com o cargo ou função para o qual tenha sido indicado</t>
         </is>
       </c>
+      <c r="ID82" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF82" t="inlineStr">
+        <is>
+          <t>A evidência apresentada, composta pelo Regimento Interno (página 3), estabelece a competência da Coordenadoria de Informática para a elaboração de Termos de Referência, mas não comprova a existência ou disponibilização de artefatos padronizados para a fase de planejamento, como modelos de DFD, ETP, Matriz de Riscos ou documentos análogos. A atribuição regimental de realizar uma atividade não equivale à disponibilização de templates ou modelos padronizados de suporte ao planejamento. Identifica-se a lacuna referente à falta de evidência da disponibilização ou existência de modelos de documentos padronizados para o planejamento dessas contratações.</t>
+        </is>
+      </c>
+      <c r="IG82" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13950,6 +14290,26 @@
           <t>possui em sua estrutura cargos ou funções formalmente atribuídas à área de segurança da informação</t>
         </is>
       </c>
+      <c r="ID85" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF85" t="inlineStr">
+        <is>
+          <t>A avaliação da Equipe de Auditoria indica que a evidência é insuficiente. Embora haja menção a minutas padronizadas em nível estadual, não constam no processo os artefatos específicos de planejamento de TI (DFD, ETP, TR ou Matriz de Riscos) adotados pelo SEPM. A evidência não demonstra a existência ou utilização desses documentos no órgão. Faltam exemplos ou modelos dos artefatos de planejamento de TI aplicados pelo auditado.</t>
+        </is>
+      </c>
+      <c r="IG85" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14544,6 +14904,26 @@
           <t>o catálogo contém as metas definidas para cada serviço (p. ex.: prazos de entrega, horários de serviço e de suporte, bem como pontos de contato para solicitação do serviço, envio de sugestões, esclarecimento de dúvidas e reporte de incidentes)</t>
         </is>
       </c>
+      <c r="ID87" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF87" t="inlineStr">
+        <is>
+          <t>Embora a norma estabeleça diretrizes para a elaboração de especificações e análises de risco (seção 6), não são disponibilizados ou referenciados modelos e artefatos padronizados para a fase de planejamento. A ausência de templates ou formulários específicos limita a efetiva padronização da documentação. A evidência é insuficiente por faltar a demonstração prática dos modelos de artefatos.</t>
+        </is>
+      </c>
+      <c r="IG87" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -15079,6 +15459,26 @@
           <t>são disponibilizados artefatos padronizados para a fase de seleção de fornecedores, como minutas, checklists, modelos de edital, pareceres, critérios de julgamento ou documentos equivalentes</t>
         </is>
       </c>
+      <c r="ID92" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF92" t="inlineStr">
+        <is>
+          <t>A evidência não demonstra a disponibilização de artefatos padronizados voltados especificamente para a fase de planejamento de contratações de TI. Embora o Decreto apresente modelos para aquisições em geral, não constam artefatos com requisitos ou especificações técnicas necessárias para TI, como critérios de segurança, interoperabilidade ou licenciamento. A documentação apresentada é genérica e insuficiente para atender às especificidades do planejamento de tecnologia. Faltam modelos de artefatos que considerem as características e exigências peculiares de bens e serviços de TI.</t>
+        </is>
+      </c>
+      <c r="IG92" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15940,6 +16340,26 @@
           <t>as áreas demandantes de soluções de TI participam do processo de planejamento de tecnologia da informação</t>
         </is>
       </c>
+      <c r="ID95" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF95" t="inlineStr">
+        <is>
+          <t>Não foram disponibilizados artefatos padronizados para a fase de planejamento das contratações de TI. O PDTIC não apresenta templates de Documento de Formalização da Demanda (DFD), Estudo Técnico Preliminar (ETP), Termo de Referência (TR) ou Matriz de Riscos. A evidência é insuficiente pela inexistência de modelos de documentos essenciais para a fase de planejamento.</t>
+        </is>
+      </c>
+      <c r="IG95" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -16279,6 +16699,26 @@
       <c r="EC98" t="inlineStr">
         <is>
           <t>há base(s) de conhecimento que registra(m) erros conhecidos e problemas, de modo a tornar eficiente e efetiva a resolução de incidentes</t>
+        </is>
+      </c>
+      <c r="ID98" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="IE98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="IF98" t="inlineStr">
+        <is>
+          <t>A Equipe de Auditoria avalia que não há comprovação de padronização documental. Não foram apresentados modelos, templates ou artefatos específicos para a fase de planejamento, coerente com a declaração de inexistência de fluxos formais registrada na página 3. A evidência é insuficiente para atestar a disponibilidade de artefatos. A lacuna reside na ausência de modelos padronizados de DFD, ETP, TR ou Matriz de Riscos.</t>
+        </is>
+      </c>
+      <c r="IG98" t="inlineStr">
+        <is>
+          <t>são disponibilizados artefatos padronizados para a fase de planejamento das contratações de TIC</t>
         </is>
       </c>
     </row>
